--- a/AAII_Financials/Quarterly/GEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>GEV</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,50 +738,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>11104000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9339000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10956000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9969000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9111000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8032000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10558000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8913000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8204000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7260000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10045000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8253000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8119000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -790,50 +794,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8709000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7474000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8616000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8057000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7241000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6508000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8447000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7656000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6487000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6006000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8304000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7152000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6947000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,50 +850,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2395000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1865000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2340000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1912000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1870000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1524000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2111000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1257000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1717000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1254000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1741000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1101000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1172000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -896,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,50 +930,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E12" s="3">
         <v>304000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>365000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>310000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>282000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>239000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>265000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>243000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>237000</v>
       </c>
       <c r="L12" s="3">
         <v>237000</v>
       </c>
       <c r="M12" s="3">
+        <v>237000</v>
+      </c>
+      <c r="N12" s="3">
         <v>255000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>223000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>216000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,50 +1040,53 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4204000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-32000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>42000</v>
       </c>
       <c r="G14" s="3">
         <v>42000</v>
       </c>
       <c r="H14" s="3">
+        <v>42000</v>
+      </c>
+      <c r="I14" s="3">
         <v>47000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-336000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1047000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>149000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>128000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-10000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,50 +1096,53 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E15" s="3">
         <v>342000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>230000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>213000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>205000</v>
       </c>
       <c r="H15" s="3">
         <v>205000</v>
       </c>
       <c r="I15" s="3">
+        <v>205000</v>
+      </c>
+      <c r="J15" s="3">
         <v>269000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>290000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>254000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>251000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>252000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>242000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>239000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1129,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,50 +1173,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10275000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8829000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10147000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9397000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8572000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7805000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9848000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8935000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7731000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7272000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9584000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8308000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8216000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,50 +1227,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>829000</v>
+      </c>
+      <c r="E18" s="3">
         <v>510000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>809000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>572000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>539000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>227000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>710000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-22000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>473000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>461000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-55000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-97000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,50 +1307,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-98000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-261000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-81000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-89000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-81000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-141000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-43000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-73000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>38000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-27000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-81000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,52 +1361,55 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="E21" s="3">
         <v>950000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1300000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>866000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>833000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>513000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1120000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>311000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>728000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>312000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>675000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>214000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>223000</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
@@ -1380,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1400,29 +1440,29 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>10000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>14000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>-18000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>21000</v>
       </c>
       <c r="O22" s="3">
         <v>21000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>21000</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1433,50 +1473,53 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>925000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5103000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1106000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>746000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>645000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>333000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1113000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-122000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1602000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-96000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>328000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,50 +1529,53 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E24" s="3">
         <v>354000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2565000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>293000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>153000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>629000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-23000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>322000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>122000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>169000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>122000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1585,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,50 +1641,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>649000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4749000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3671000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>453000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>492000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>265000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>484000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-99000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1280000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-106000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-185000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-148000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,50 +1697,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4745000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3664000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>452000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>514000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>254000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>484000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-96000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1294000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-130000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>197000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-170000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-150000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,50 +1977,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E32" s="3">
         <v>98000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>261000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>81000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>89000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>81000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>141000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>43000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>73000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-38000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>27000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>81000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1963,50 +2033,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4745000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3664000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>452000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>514000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>254000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>484000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-96000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1294000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-130000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>197000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-170000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-150000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,50 +2145,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4745000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3664000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>452000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>514000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>254000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>484000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-96000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1294000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-130000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>197000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-170000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-150000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,44 +2308,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12720000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9772000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8469000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7545000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7492000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7807000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7767000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7395000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5779000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3255000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1501000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2362,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2284,11 +2374,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>466000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2328,44 +2418,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18736000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17361000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17380000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15393000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15078000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14763000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15284000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15007000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14280000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14858000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15045000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2381,44 +2474,47 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12692000</v>
+      </c>
+      <c r="E44" s="3">
         <v>11919000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10429000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10032000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9825000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9156000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8587000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9377000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9346000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8859000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8253000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,44 +2530,47 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2885000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3517000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2395000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2908000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1914000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1910000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1779000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1362000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1317000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2271000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2451000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,44 +2586,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>47433000</v>
+      </c>
+      <c r="E46" s="3">
         <v>42969000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40216000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36278000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34709000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33936000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34153000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33141000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30722000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29243000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27428000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2540,44 +2642,47 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1396000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1834000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1916000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2170000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2137000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2149000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2376000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2405000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3647000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3555000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,44 +2698,47 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7354000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7139000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6006000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5555000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5419000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5225000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5150000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5148000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5168000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5224000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5228000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,49 +2754,52 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14196000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14398000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5166000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5074000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5267000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5141000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5076000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5313000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5279000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5394000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5479000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2699,8 +2810,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,44 +2922,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4188000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4066000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4064000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3405000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3284000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2976000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2623000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2758000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2481000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2303000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2096000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,44 +3034,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>80800000</v>
+      </c>
+      <c r="E54" s="3">
         <v>75612000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>63016000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54398000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53078000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51559000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51485000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>50853000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48052000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47872000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46121000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,44 +3136,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8710000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8137000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7264000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8059000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7582000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6919000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7016000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7442000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6326000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7509000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4735000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,20 +3190,23 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E58" s="3">
         <v>51000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>270000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -3080,11 +3214,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>241000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -3092,19 +3226,19 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>365000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3112,44 +3246,47 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46790000</v>
+      </c>
+      <c r="E59" s="3">
         <v>39592000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30958000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26941000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25923000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25438000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22229000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23374000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22281000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22007000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22126000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,44 +3302,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55830000</v>
+      </c>
+      <c r="E60" s="3">
         <v>48094000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40972000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35272000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33761000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32677000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31685000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31233000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29065000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29516000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29306000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,44 +3358,47 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3665000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3704000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>926000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1080000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1059000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1013000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>820000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>983000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>979000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1021000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>819000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3271,44 +3414,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6719000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7451000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7485000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7497000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7493000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7415000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7403000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7296000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7285000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6931000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7061000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,44 +3638,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67685000</v>
+      </c>
+      <c r="E66" s="3">
         <v>60547000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50720000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44669000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43131000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41887000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40892000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40335000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38003000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37891000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37741000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,38 +3940,41 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11296000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10762000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6154000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2626000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2241000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1865000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1611000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1198000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1294000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,44 +4164,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11957000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13922000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11178000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8646000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8877000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8607000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9546000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9504000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9067000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8974000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7416000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,50 +4337,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4745000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3664000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>452000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>514000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>254000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>484000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-96000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1294000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-130000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>197000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-170000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-150000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,41 +4417,42 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E83" s="3">
         <v>149000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>180000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>228000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>191000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>188000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>193000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>184000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>171000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>176000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4272,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,50 +4751,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5492000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5188000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2479000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>980000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>367000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1161000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>921000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1127000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>979000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-444000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1931000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>233000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-288000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,52 +4831,53 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-386000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-397000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-671000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-247000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-173000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-186000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-350000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-159000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-157000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-217000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-280000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-181000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-159000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -4664,8 +4885,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,50 +4997,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-374000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-167000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-121000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-93000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-175000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>537000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-285000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-257000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,29 +5077,30 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E96" s="3">
         <v>137000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>68000</v>
       </c>
       <c r="F96" s="3">
         <v>68000</v>
       </c>
       <c r="G96" s="3">
+        <v>68000</v>
+      </c>
+      <c r="H96" s="3">
         <v>70000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>69000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
@@ -4888,8 +5122,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -4897,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,50 +5299,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2743000</v>
+      </c>
+      <c r="E100" s="3">
         <v>442000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1178000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-774000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-604000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1257000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>163000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>585000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>970000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1934000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1064000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-286000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>238000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,41 +5355,44 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E101" s="3">
         <v>90000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-99000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-32000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>44000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-31000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>13000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5162,57 +5411,63 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2948000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1323000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>901000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>54000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-213000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-99000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>810000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1616000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2452000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1173000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>654000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-120000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-454000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
